--- a/ig/TEST-SUPPLEMENT/CodeSystem-TRE-R286-TypeFermeture.xlsx
+++ b/ig/TEST-SUPPLEMENT/CodeSystem-TRE-R286-TypeFermeture.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="76">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250915120000</t>
+    <t>20251016120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-15T12:00:00+01:00</t>
+    <t>2025-10-16T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -199,6 +199,9 @@
     <t>Définitive</t>
   </si>
   <si>
+    <t>Désigne la fermeture définitive d’un élément de l’organisation interne d’un établissement de santé</t>
+  </si>
+  <si>
     <t>ERR</t>
   </si>
   <si>
@@ -229,10 +232,16 @@
     <t>Provisoire</t>
   </si>
   <si>
+    <t>Désigne la fermeture provisoire d’un élément de l’organisation interne d’un établissement santé. L’utilisateur du référentiel ROR qui sélectionne cette valeur doit alors obligatoirement renseigner une date de réouverture de l’élément en question.</t>
+  </si>
+  <si>
     <t>PRE</t>
   </si>
   <si>
     <t>Prévisionnelle</t>
+  </si>
+  <si>
+    <t>Désigne la fermeture prévisionnelle d’un élément de l’organisation interne d’un établissement santé. L’utilisateur du référentiel ROR qui sélectionne cette valeur a alors la possibilité de renseigner une date de réouverture de l’élément en question.</t>
   </si>
 </sst>
 </file>
@@ -669,17 +678,19 @@
       <c r="C2" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>61</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -688,10 +699,10 @@
         <v>58</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -700,10 +711,10 @@
         <v>58</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -712,10 +723,10 @@
         <v>58</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -724,24 +735,28 @@
         <v>58</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>72</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
         <v>58</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
